--- a/output/月度核算报表_Phase2.xlsx
+++ b/output/月度核算报表_Phase2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平台收入汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仓库成本汇总" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="综合损益概览" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="限制说明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="平台收入汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="仓库成本汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="综合损益概览" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="限制说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Boutique local 11月 Detail-1764659035833-e7d1</t>
+          <t>Boutique local</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6924,7 +6924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7060,12 +7060,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>TLB账单</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7074,7 +7074,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4216.3</v>
+        <v>4637.25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -7096,24 +7096,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6164.56</v>
+        <v>4216.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LHZ</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7136,7 +7136,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1294.76022592</v>
+        <v>6164.56</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -7158,27 +7158,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>LHZ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12974.07</v>
+        <v>1294.76022592</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>TLB账单</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7198,7 +7198,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1986</v>
+        <v>5933.18300000002</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -7215,12 +7215,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10464.043</v>
+        <v>12974.07</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -7237,41 +7237,41 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8928.690000000001</v>
+        <v>1986</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -7282,20 +7282,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LHZ</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3978.276000000003</v>
+        <v>10464.043</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -7313,27 +7313,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>49557.69</v>
+        <v>8928.690000000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -7344,24 +7344,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>LHZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1324.592</v>
+        <v>3978.276000000003</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -7370,12 +7370,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14245.328</v>
+        <v>49557.69</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -7392,41 +7392,41 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8791.209999999999</v>
+        <v>1324.592</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -7437,20 +7437,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LHZ</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2220.551</v>
+        <v>14245.328</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -7468,27 +7468,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>23590.24</v>
+        <v>8791.209999999999</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>618</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -7499,24 +7499,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>LHZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>880.22</v>
+        <v>2220.551</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>409</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -7525,12 +7525,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20368.098</v>
+        <v>23590.24</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -7547,41 +7547,41 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>618</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25294.74</v>
+        <v>880.22</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>409</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -7592,20 +7592,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LHZ</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2239.845999999999</v>
+        <v>20368.098</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -7623,27 +7623,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>104848.22351</v>
+        <v>25294.74</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3696</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -7654,24 +7654,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>LHZ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>767.347</v>
+        <v>2239.845999999999</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>335</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -7680,12 +7680,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12672.069</v>
+        <v>104848.22351</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -7702,41 +7702,41 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>3696</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>19513.48</v>
+        <v>767.347</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>335</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -7747,20 +7747,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LHZ</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1340.964</v>
+        <v>12672.069</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -7778,27 +7778,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>75399.54442000001</v>
+        <v>19513.48</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2536</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -7809,24 +7809,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>LHZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>845.999</v>
+        <v>1340.964</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>481</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -7835,12 +7835,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>17542.4</v>
+        <v>75399.54442000001</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -7857,41 +7857,41 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>2536</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19563.59</v>
+        <v>845.999</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>481</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -7902,20 +7902,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LHZ</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1867.9</v>
+        <v>17542.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -7933,27 +7933,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>78624.71593000001</v>
+        <v>19563.59</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2314</v>
+        <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -7964,27 +7964,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>LHZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1464.63</v>
+        <v>1867.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1067.617</v>
+        <v>78624.71593000001</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -8012,72 +8012,72 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>542</v>
+        <v>2314</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>18999.808</v>
+        <v>1464.63</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16425.57</v>
+        <v>1067.617</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>542</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -8088,20 +8088,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LHZ</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2704.83</v>
+        <v>18999.808</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -8119,27 +8119,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>74440.86003</v>
+        <v>16425.57</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3429</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -8150,27 +8150,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>LHZ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>940.73</v>
+        <v>2704.83</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1300.14</v>
+        <v>74440.86003</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -8198,72 +8198,72 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>765</v>
+        <v>3429</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13763.771</v>
+        <v>940.73</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>22946.23</v>
+        <v>1300.14</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>765</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -8274,20 +8274,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LHZ</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1279.189</v>
+        <v>13763.771</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -8305,27 +8305,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>79514.83893</v>
+        <v>22946.23</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>5245</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -8336,24 +8336,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>LHZ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2111.75</v>
+        <v>1279.189</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -8367,24 +8367,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3721.64</v>
+        <v>79514.83893</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>5245</v>
       </c>
       <c r="G47" t="n">
         <v>4</v>
@@ -8398,24 +8398,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1809.852</v>
+        <v>2111.75</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>237</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -8429,55 +8429,55 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>868.971</v>
+        <v>3721.64</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>372</v>
+        <v>4</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>奥韵汇</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14119.885</v>
+        <v>1809.852</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -8486,32 +8486,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>17294.51</v>
+        <v>868.971</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>372</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -8522,20 +8522,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LHZ</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1384</v>
+        <v>14119.885</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -8553,27 +8553,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>71877.39468</v>
+        <v>17294.51</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>4211</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -8584,24 +8584,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>LHZ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1495.02</v>
+        <v>1384</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1853</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -8615,27 +8615,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2016.97</v>
+        <v>71877.39468</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>4211</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -8646,24 +8646,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4848.367</v>
+        <v>1495.02</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2410</v>
+        <v>1853</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -8677,55 +8677,55 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1122.2</v>
+        <v>2016.97</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>596</v>
+        <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>奥韵汇</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>8288.278</v>
+        <v>4848.367</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>2410</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -8734,63 +8734,63 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>19891.91</v>
+        <v>1122.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>596</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>西邮</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>43962.43333</v>
+        <v>300.142</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2340</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -8801,24 +8801,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2422.61</v>
+        <v>8288.278</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3159</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
@@ -8832,27 +8832,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2456.2</v>
+        <v>19891.91</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -8863,27 +8863,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2896.502</v>
+        <v>43962.43333</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1783</v>
+        <v>2340</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -8894,24 +8894,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>549.703</v>
+        <v>2422.61</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>311</v>
+        <v>3159</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -8920,43 +8920,43 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12431.467</v>
+        <v>2456.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>奥韵汇</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>29861.77</v>
+        <v>2896.502</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -8973,21 +8973,21 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1783</v>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>35225.48926</v>
+        <v>549.703</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -9004,38 +9004,38 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1543</v>
+        <v>311</v>
       </c>
       <c r="G67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>西邮</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1450.35</v>
+        <v>188.23163344</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3284</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -9049,27 +9049,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2494.16</v>
+        <v>12431.467</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2427.939</v>
+        <v>29861.77</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -9097,10 +9097,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2552</v>
+        <v>2</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>377.689</v>
+        <v>35225.48926</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -9128,38 +9128,38 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>204</v>
+        <v>1543</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>17453.191</v>
+        <v>1450.35</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>3284</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -9168,91 +9168,91 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>16777.09</v>
+        <v>2494.16</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>奥韵汇</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>38273.66821</v>
+        <v>2427.939</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2097</v>
+        <v>2552</v>
       </c>
       <c r="G74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2597.11</v>
+        <v>377.689</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1906</v>
+        <v>204</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -9261,32 +9261,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>西邮</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2349.69</v>
+        <v>1150.74105</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -9297,27 +9297,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13749.342</v>
+        <v>17453.191</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2263</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -9328,38 +9328,38 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>353.945</v>
+        <v>16777.09</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>17302.714</v>
+        <v>38273.66821</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -9376,189 +9376,189 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>2097</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>8786.41</v>
+        <v>2597.11</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>1906</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>35526.95081</v>
+        <v>2349.69</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2656</v>
+        <v>4</v>
       </c>
       <c r="G81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>奥韵汇</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1025.5</v>
+        <v>13749.342</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1215</v>
+        <v>2263</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>易达云</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3175.66</v>
+        <v>1106.73</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2386.464</v>
+        <v>353.945</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>4154</v>
+        <v>186</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>西邮</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1123.99</v>
+        <v>2177.8807813</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -9571,7 +9571,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9585,7 +9585,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>26185.921</v>
+        <v>17302.714</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4655.58</v>
+        <v>8786.41</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9647,7 +9647,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>24487.77449</v>
+        <v>35526.95081</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -9655,16 +9655,16 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1361</v>
+        <v>2656</v>
       </c>
       <c r="G88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2266.86</v>
+        <v>1025.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2725</v>
+        <v>1215</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -9695,7 +9695,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1599.84</v>
+        <v>3175.66</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -9717,16 +9717,16 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9740,7 +9740,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11170.955</v>
+        <v>2386.464</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>6864</v>
+        <v>4154</v>
       </c>
       <c r="G91" t="n">
         <v>2</v>
@@ -9757,60 +9757,60 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>易达云</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>24297.43502</v>
+        <v>335.84</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1706</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>625.89</v>
+        <v>1123.99</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1435</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
@@ -9819,63 +9819,714 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>西邮</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1158.42</v>
+        <v>1229.5804679</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>26185.921</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>4655.58</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>TSP</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>24487.77449</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1361</v>
+      </c>
+      <c r="G97" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>东方嘉盛</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>2266.86</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>2725</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1599.84</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>2</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>奥韵汇</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11170.955</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>6864</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>易达云</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>47.725</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>西邮</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>757.8144600000001</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>TSP</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>24297.43502</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1706</v>
+      </c>
+      <c r="G103" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>东方嘉盛</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>625.89</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1435</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1158.42</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>3</v>
+      </c>
+      <c r="G105" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
         <is>
           <t>奥韵汇</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D106" t="n">
         <v>12321.804</v>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="F95" t="n">
+      <c r="F106" t="n">
         <v>10027</v>
       </c>
-      <c r="G95" t="n">
+      <c r="G106" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>易达云</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>175.83</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>易领</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>2911.7467</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>4</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>津达</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>78069.496</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>19369</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>久喜</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>5600735.95</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>381</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>酷麓</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1532.519</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>963</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>MIC</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>MIC</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>MIC</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>MIC</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>MIC</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9889,7 +10540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9929,10 +10580,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>11155.207</v>
+        <v>15792.457</v>
       </c>
       <c r="D2" t="n">
-        <v>-11155.207</v>
+        <v>-15792.457</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -9950,10 +10601,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>26635.69022592</v>
+        <v>32568.87322592002</v>
       </c>
       <c r="D3" t="n">
-        <v>-26635.69022592</v>
+        <v>-32568.87322592002</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -10052,17 +10703,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>20446.97</v>
       </c>
       <c r="C8" t="n">
         <v>120130.85293</v>
       </c>
       <c r="D8" t="n">
-        <v>-120130.85293</v>
+        <v>-99683.88293000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>⚠️ 该月无平台收入数据</t>
+          <t>不含SKU采购成本</t>
         </is>
       </c>
     </row>
@@ -10073,13 +10724,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132911.19</v>
+        <v>112464.22</v>
       </c>
       <c r="C9" t="n">
         <v>114811.93803</v>
       </c>
       <c r="D9" t="n">
-        <v>18099.25197</v>
+        <v>-2347.71803</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -10115,13 +10766,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>609727.1800000001</v>
+        <v>653539.65</v>
       </c>
       <c r="C11" t="n">
-        <v>114158.34668</v>
+        <v>114458.48868</v>
       </c>
       <c r="D11" t="n">
-        <v>495568.83332</v>
+        <v>539081.16132</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -10136,13 +10787,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>987582.86</v>
+        <v>960438.62</v>
       </c>
       <c r="C12" t="n">
-        <v>80467.63632999999</v>
+        <v>80655.86796344</v>
       </c>
       <c r="D12" t="n">
-        <v>907115.22367</v>
+        <v>879782.75203656</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -10157,13 +10808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>640398.6800000001</v>
+        <v>639540.6800000001</v>
       </c>
       <c r="C13" t="n">
-        <v>84268.86426</v>
+        <v>85419.60531</v>
       </c>
       <c r="D13" t="n">
-        <v>556129.81574</v>
+        <v>554121.07469</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -10178,13 +10829,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>784935.85</v>
+        <v>758146.83</v>
       </c>
       <c r="C14" t="n">
-        <v>91554.03621000001</v>
+        <v>94838.6469913</v>
       </c>
       <c r="D14" t="n">
-        <v>693381.81379</v>
+        <v>663308.1830087</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -10199,13 +10850,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>913068.66</v>
+        <v>914637.74</v>
       </c>
       <c r="C15" t="n">
-        <v>69327.68881000001</v>
+        <v>70893.1092779</v>
       </c>
       <c r="D15" t="n">
-        <v>843740.97119</v>
+        <v>843744.6307221</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -10220,13 +10871,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1452083.64</v>
+        <v>1461493.35</v>
       </c>
       <c r="C16" t="n">
-        <v>70366.93049</v>
+        <v>71172.46995</v>
       </c>
       <c r="D16" t="n">
-        <v>1381716.70951</v>
+        <v>1390320.88005</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -10244,12 +10895,138 @@
         <v>1025032.68</v>
       </c>
       <c r="C17" t="n">
-        <v>38403.54902</v>
+        <v>119560.62172</v>
       </c>
       <c r="D17" t="n">
-        <v>986629.13098</v>
+        <v>905472.05828</v>
       </c>
       <c r="E17" t="inlineStr">
+        <is>
+          <t>不含SKU采购成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5602268.469</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-5602268.469</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>⚠️ 该月无平台收入数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>不含SKU采购成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>不含SKU采购成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>不含SKU采购成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>不含SKU采购成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>不含SKU采购成本</t>
         </is>

--- a/output/月度核算报表_Phase2.xlsx
+++ b/output/月度核算报表_Phase2.xlsx
@@ -6924,7 +6924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7742,32 +7742,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>澳洲FDM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12672.069</v>
+        <v>4074.05</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -7778,27 +7778,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>19513.48</v>
+        <v>12672.069</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LHZ</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1340.964</v>
+        <v>19513.48</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -7840,27 +7840,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>LHZ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>75399.54442000001</v>
+        <v>1340.964</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2536</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>845.999</v>
+        <v>75399.54442000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -7888,34 +7888,34 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>481</v>
+        <v>2536</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>中转仓</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>17542.4</v>
+        <v>2565.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -7928,63 +7928,63 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>19563.59</v>
+        <v>845.999</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>481</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LHZ</t>
+          <t>澳洲FDM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1867.9</v>
+        <v>1629.62</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>78624.71593000001</v>
+        <v>17542.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -8012,10 +8012,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2314</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -8026,27 +8026,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1464.63</v>
+        <v>19563.59</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -8057,24 +8057,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>LHZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1067.617</v>
+        <v>1867.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>542</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -8083,12 +8083,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>18999.808</v>
+        <v>78624.71593000001</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -8105,38 +8105,38 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>2314</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>sphere freight</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>16425.57</v>
+        <v>3052.95</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
         <v>2</v>
@@ -8145,43 +8145,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LHZ</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2704.83</v>
+        <v>1464.63</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>74440.86003</v>
+        <v>1067.617</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -8198,34 +8198,34 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3429</v>
+        <v>542</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>澳洲FDM</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>940.73</v>
+        <v>3259.24</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8252,7 +8252,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1300.14</v>
+        <v>18999.808</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>765</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -8269,43 +8269,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13763.771</v>
+        <v>16425.57</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>LHZ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8314,7 +8314,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>22946.23</v>
+        <v>2704.83</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -8325,89 +8325,89 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LHZ</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1279.189</v>
+        <v>74440.86003</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>3429</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>sphere freight</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>79514.83893</v>
+        <v>1783</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>5245</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2111.75</v>
+        <v>940.73</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -8415,72 +8415,72 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3721.64</v>
+        <v>1300.14</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>765</v>
       </c>
       <c r="G49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>澳洲FDM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1809.852</v>
+        <v>3275.14</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>237</v>
+        <v>4</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>868.971</v>
+        <v>13763.771</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>372</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -8517,43 +8517,43 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>14119.885</v>
+        <v>22946.23</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>LHZ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -8562,7 +8562,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>17294.51</v>
+        <v>1279.189</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -8573,75 +8573,75 @@
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LHZ</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1384</v>
+        <v>79514.83893</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>5245</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>sphere freight</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>71877.39468</v>
+        <v>260</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>4211</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1495.02</v>
+        <v>2111.75</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1853</v>
+        <v>3</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -8672,7 +8672,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2016.97</v>
+        <v>3721.64</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -8694,16 +8694,16 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8717,7 +8717,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4848.367</v>
+        <v>1809.852</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2410</v>
+        <v>237</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -8734,7 +8734,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1122.2</v>
+        <v>868.971</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>596</v>
+        <v>372</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -8765,38 +8765,38 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>西邮</t>
+          <t>澳洲FDM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>300.142</v>
+        <v>4132.29</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8810,7 +8810,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>8288.278</v>
+        <v>14119.885</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8841,7 +8841,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>19891.91</v>
+        <v>17294.51</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -8858,87 +8858,87 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>LHZ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>43962.43333</v>
+        <v>1384</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2340</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2422.61</v>
+        <v>71877.39468</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3159</v>
+        <v>4211</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>sphere freight</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2456.2</v>
+        <v>2162.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -8951,29 +8951,29 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2896.502</v>
+        <v>1495.02</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1783</v>
+        <v>1853</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -8982,60 +8982,60 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>549.703</v>
+        <v>2016.97</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>311</v>
+        <v>3</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>西邮</t>
+          <t>奥韵汇</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>188.23163344</v>
+        <v>4848.367</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>2410</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -9044,12 +9044,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12431.467</v>
+        <v>1122.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>596</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -9075,91 +9075,91 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>澳洲FDM</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>29861.77</v>
+        <v>4308.54</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>西邮</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>35225.48926</v>
+        <v>300.142</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1543</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1450.35</v>
+        <v>8288.278</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3284</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -9168,91 +9168,91 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2494.16</v>
+        <v>19891.91</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2427.939</v>
+        <v>43962.43333</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2552</v>
+        <v>2340</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>377.689</v>
+        <v>2422.61</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>204</v>
+        <v>3159</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -9261,60 +9261,60 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>西邮</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1150.74105</v>
+        <v>2456.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>奥韵汇</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>17453.191</v>
+        <v>2896.502</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>1783</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -9323,91 +9323,91 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>16777.09</v>
+        <v>549.703</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>311</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>澳洲FDM</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>38273.66821</v>
+        <v>3084.08</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2097</v>
+        <v>5</v>
       </c>
       <c r="G79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>西邮</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2597.11</v>
+        <v>188.23163344</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1906</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
@@ -9416,43 +9416,43 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2349.69</v>
+        <v>12431.467</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13749.342</v>
+        <v>29861.77</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -9469,69 +9469,69 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2263</v>
+        <v>2</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>易达云</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1106.73</v>
+        <v>35225.48926</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>1543</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>353.945</v>
+        <v>1450.35</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>186</v>
+        <v>3284</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -9540,60 +9540,60 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>西邮</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2177.8807813</v>
+        <v>2494.16</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>奥韵汇</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>17302.714</v>
+        <v>2427.939</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>2552</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -9602,91 +9602,91 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>8786.41</v>
+        <v>377.689</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>澳洲FDM</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>35526.95081</v>
+        <v>2137.56</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2656</v>
+        <v>4</v>
       </c>
       <c r="G88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>西邮</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1025.5</v>
+        <v>1150.74105</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1215</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -9695,43 +9695,43 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3175.66</v>
+        <v>17453.191</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9740,7 +9740,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2386.464</v>
+        <v>16777.09</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>4154</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
         <v>2</v>
@@ -9757,91 +9757,91 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>易达云</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>335.84</v>
+        <v>38273.66821</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>2097</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>sphere freight</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1123.99</v>
+        <v>2316</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>西邮</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1229.5804679</v>
+        <v>2597.11</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>1906</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
@@ -9850,43 +9850,43 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>26185.921</v>
+        <v>2349.69</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>奥韵汇</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>4655.58</v>
+        <v>13749.342</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>2263</v>
       </c>
       <c r="G96" t="n">
         <v>2</v>
@@ -9912,60 +9912,60 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>易达云</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>24487.77449</v>
+        <v>1106.73</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1361</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2266.86</v>
+        <v>353.945</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2725</v>
+        <v>186</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
@@ -9974,87 +9974,87 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>澳洲FDM</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1599.84</v>
+        <v>2137.56</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>西邮</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11170.955</v>
+        <v>2177.8807813</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>6864</v>
+        <v>1</v>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>易达云</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>47.725</v>
+        <v>17302.714</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -10067,38 +10067,38 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>西邮</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>757.8144600000001</v>
+        <v>8786.41</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F102" t="n">
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>24297.43502</v>
+        <v>35526.95081</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -10120,38 +10120,38 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1706</v>
+        <v>2656</v>
       </c>
       <c r="G103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>sphere freight</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>625.89</v>
+        <v>960</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1435</v>
+        <v>1</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
@@ -10160,21 +10160,21 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1158.42</v>
+        <v>1025.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -10182,83 +10182,83 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1215</v>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12321.804</v>
+        <v>3175.66</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>10027</v>
+        <v>4</v>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>易达云</t>
+          <t>奥韵汇</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>175.83</v>
+        <v>2386.464</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>4154</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>易领</t>
+          <t>易达云</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2911.7467</v>
+        <v>335.84</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -10284,29 +10284,29 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>津达</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>78069.496</v>
+        <v>1123.99</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>19369</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
         <v>1</v>
@@ -10315,43 +10315,43 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>久喜</t>
+          <t>澳洲FDM</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>5600735.95</v>
+        <v>761.91</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>381</v>
+        <v>3</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>酷麓</t>
+          <t>西邮</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -10360,7 +10360,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1532.519</v>
+        <v>1229.5804679</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>963</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -10377,29 +10377,29 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MIC</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>26185.921</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -10408,12 +10408,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MIC</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -10422,7 +10422,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>4655.58</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -10430,102 +10430,505 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MIC</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>24487.77449</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>1361</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MIC</t>
+          <t>sphere freight</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>2089</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MIC</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>2266.86</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>2725</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1599.84</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>2</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>奥韵汇</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="D116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" t="inlineStr">
+      <c r="D118" t="n">
+        <v>11170.955</v>
+      </c>
+      <c r="E118" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" t="n">
+      <c r="F118" t="n">
+        <v>6864</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>易达云</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>47.725</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>西邮</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>757.8144600000001</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TSP</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>24297.43502</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1706</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>东方嘉盛</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>625.89</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1435</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1158.42</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>3</v>
+      </c>
+      <c r="G123" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>奥韵汇</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>12321.804</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>10027</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>易达云</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>175.83</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>易领</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>2911.7467</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>4</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>津达</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>78069.496</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>19369</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>久喜</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>5600735.95</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>381</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>酷麓</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1532.519</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>963</v>
+      </c>
+      <c r="G129" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10540,7 +10943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10664,10 +11067,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>153518.25451</v>
+        <v>157592.30451</v>
       </c>
       <c r="D6" t="n">
-        <v>-153518.25451</v>
+        <v>-157592.30451</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -10685,10 +11088,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>109772.05642</v>
+        <v>113967.17642</v>
       </c>
       <c r="D7" t="n">
-        <v>-109772.05642</v>
+        <v>-113967.17642</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -10706,10 +11109,10 @@
         <v>20446.97</v>
       </c>
       <c r="C8" t="n">
-        <v>120130.85293</v>
+        <v>126443.04293</v>
       </c>
       <c r="D8" t="n">
-        <v>-99683.88293000001</v>
+        <v>-105996.07293</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -10727,10 +11130,10 @@
         <v>112464.22</v>
       </c>
       <c r="C9" t="n">
-        <v>114811.93803</v>
+        <v>119870.07803</v>
       </c>
       <c r="D9" t="n">
-        <v>-2347.71803</v>
+        <v>-7405.85803</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -10748,10 +11151,10 @@
         <v>748052.41</v>
       </c>
       <c r="C10" t="n">
-        <v>126016.24193</v>
+        <v>130408.53193</v>
       </c>
       <c r="D10" t="n">
-        <v>622036.16807</v>
+        <v>617643.87807</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -10769,10 +11172,10 @@
         <v>653539.65</v>
       </c>
       <c r="C11" t="n">
-        <v>114458.48868</v>
+        <v>120929.42868</v>
       </c>
       <c r="D11" t="n">
-        <v>539081.16132</v>
+        <v>532610.22132</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -10790,10 +11193,10 @@
         <v>960438.62</v>
       </c>
       <c r="C12" t="n">
-        <v>80655.86796344</v>
+        <v>83739.94796344</v>
       </c>
       <c r="D12" t="n">
-        <v>879782.75203656</v>
+        <v>876698.67203656</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -10811,10 +11214,10 @@
         <v>639540.6800000001</v>
       </c>
       <c r="C13" t="n">
-        <v>85419.60531</v>
+        <v>87557.16531</v>
       </c>
       <c r="D13" t="n">
-        <v>554121.07469</v>
+        <v>551983.51469</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -10832,10 +11235,10 @@
         <v>758146.83</v>
       </c>
       <c r="C14" t="n">
-        <v>94838.6469913</v>
+        <v>99292.2069913</v>
       </c>
       <c r="D14" t="n">
-        <v>663308.1830087</v>
+        <v>658854.6230087</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -10853,10 +11256,10 @@
         <v>914637.74</v>
       </c>
       <c r="C15" t="n">
-        <v>70893.1092779</v>
+        <v>72615.01927790001</v>
       </c>
       <c r="D15" t="n">
-        <v>843744.6307221</v>
+        <v>842022.7207221</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -10874,10 +11277,10 @@
         <v>1461493.35</v>
       </c>
       <c r="C16" t="n">
-        <v>71172.46995</v>
+        <v>73261.46995</v>
       </c>
       <c r="D16" t="n">
-        <v>1390320.88005</v>
+        <v>1388231.88005</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -10924,111 +11327,6 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>⚠️ 该月无平台收入数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>不含SKU采购成本</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>不含SKU采购成本</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>不含SKU采购成本</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>不含SKU采购成本</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>不含SKU采购成本</t>
         </is>
       </c>
     </row>

--- a/output/月度核算报表_Phase2.xlsx
+++ b/output/月度核算报表_Phase2.xlsx
@@ -7004,7 +7004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G176"/>
+  <dimension ref="A1:G184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>23590.24</v>
+        <v>59724.55516</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>618</v>
+        <v>1923</v>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>80275.60000000001</v>
+        <v>85465.60000000001</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>141391.34</v>
+        <v>142191.34</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -10741,27 +10741,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>上海货盘</t>
+          <t>mic</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>145663.88</v>
+        <v>1632</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -10781,18 +10781,18 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>888</v>
+        <v>145663.88</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F122" t="n">
+        <v>38</v>
+      </c>
+      <c r="G122" t="n">
         <v>3</v>
-      </c>
-      <c r="G122" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>上海货盘</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -10812,15 +10812,15 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1450.35</v>
+        <v>888</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>3284</v>
+        <v>3</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -10834,16 +10834,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2494.16</v>
+        <v>1450.35</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -10851,10 +10851,10 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>4</v>
+        <v>3284</v>
       </c>
       <c r="G124" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -10865,27 +10865,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2427.939</v>
+        <v>2494.16</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2552</v>
+        <v>4</v>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126">
@@ -10896,24 +10896,24 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>奥韵汇</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>377.689</v>
+        <v>2427.939</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>204</v>
+        <v>2552</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -10927,27 +10927,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>澳洲FDM</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2137.56</v>
+        <v>377.689</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>4</v>
+        <v>204</v>
       </c>
       <c r="G127" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -10958,51 +10958,51 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>西邮</t>
+          <t>澳洲FDM</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1150.74105</v>
+        <v>2137.56</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>西邮</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>17453.191</v>
+        <v>1150.74105</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -11020,27 +11020,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>16777.09</v>
+        <v>17453.191</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F130" t="n">
         <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -11051,27 +11051,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>38273.66821</v>
+        <v>16777.09</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2097</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -11082,27 +11082,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>sphere freight</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>2316</v>
+        <v>38273.66821</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>2097</v>
       </c>
       <c r="G132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
@@ -11113,27 +11113,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>上海货盘</t>
+          <t>mic</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>170266.62</v>
+        <v>5868.69196</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -11144,16 +11144,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>上海货盘</t>
+          <t>sphere freight</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11865.27</v>
+        <v>2316</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G134" t="n">
         <v>3</v>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>上海货盘</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -11184,7 +11184,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2597.11</v>
+        <v>170266.62</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -11192,10 +11192,10 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1906</v>
+        <v>27</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136">
@@ -11206,27 +11206,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>上海货盘</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2349.69</v>
+        <v>11865.27</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
@@ -11237,27 +11237,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>13749.342</v>
+        <v>2597.11</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>2263</v>
+        <v>1906</v>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -11268,27 +11268,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>易达云</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1106.73</v>
+        <v>2349.69</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
@@ -11299,27 +11299,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>奥韵汇</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>353.945</v>
+        <v>13749.342</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>186</v>
+        <v>2263</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -11330,27 +11330,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>澳洲FDM</t>
+          <t>易达云</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2137.56</v>
+        <v>1106.73</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -11361,24 +11361,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>西邮</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2177.8807813</v>
+        <v>353.945</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="G141" t="n">
         <v>1</v>
@@ -11387,63 +11387,63 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>澳洲FDM</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>17302.714</v>
+        <v>2137.56</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>西邮</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>8786.41</v>
+        <v>2177.8807813</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F143" t="n">
         <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>35526.95081</v>
+        <v>17302.714</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -11471,10 +11471,10 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>2656</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -11485,27 +11485,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>sphere freight</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>960</v>
+        <v>8786.41</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F145" t="n">
         <v>1</v>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -11516,27 +11516,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>上海货盘</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>215215.31</v>
+        <v>35526.95081</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>22</v>
+        <v>2656</v>
       </c>
       <c r="G146" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147">
@@ -11547,27 +11547,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>上海货盘</t>
+          <t>mic</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>15346.5031681896</v>
+        <v>5902.5579034</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -11578,24 +11578,24 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>sphere freight</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1025.5</v>
+        <v>960</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1215</v>
+        <v>1</v>
       </c>
       <c r="G148" t="n">
         <v>1</v>
@@ -11609,16 +11609,16 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>上海货盘</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>3175.66</v>
+        <v>215215.31</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G149" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150">
@@ -11640,27 +11640,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>上海货盘</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2386.464</v>
+        <v>15346.5031681896</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>4154</v>
+        <v>54</v>
       </c>
       <c r="G150" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
@@ -11671,24 +11671,24 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>易达云</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>335.84</v>
+        <v>1025.5</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>1215</v>
       </c>
       <c r="G151" t="n">
         <v>1</v>
@@ -11702,27 +11702,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1123.99</v>
+        <v>3175.66</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G152" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153">
@@ -11733,27 +11733,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>澳洲FDM</t>
+          <t>奥韵汇</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>761.91</v>
+        <v>2386.464</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>3</v>
+        <v>4154</v>
       </c>
       <c r="G153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>西邮</t>
+          <t>易达云</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -11773,7 +11773,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1229.5804679</v>
+        <v>335.84</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -11790,12 +11790,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -11804,7 +11804,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>26185.921</v>
+        <v>1123.99</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -11821,60 +11821,60 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>4655.58</v>
+        <v>357.75</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F156" t="n">
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>澳洲FDM</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>24487.77449</v>
+        <v>1015.88</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1361</v>
+        <v>4</v>
       </c>
       <c r="G157" t="n">
         <v>4</v>
@@ -11883,21 +11883,21 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>sphere freight</t>
+          <t>西邮</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2089</v>
+        <v>1229.5804679</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -11905,10 +11905,10 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -11919,27 +11919,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>上海货盘</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>149006.67</v>
+        <v>26185.921</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -11950,27 +11950,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>上海货盘</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>7547.36</v>
+        <v>4655.58</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -11981,27 +11981,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>2266.86</v>
+        <v>24487.77449</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>2725</v>
+        <v>1361</v>
       </c>
       <c r="G161" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162">
@@ -12012,27 +12012,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>mic</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1599.84</v>
+        <v>5370.757690425</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -12043,27 +12043,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>sphere freight</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>11170.955</v>
+        <v>2089</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>6864</v>
+        <v>3</v>
       </c>
       <c r="G163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -12074,27 +12074,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>易达云</t>
+          <t>上海货盘</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>47.725</v>
+        <v>149006.67</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="G164" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165">
@@ -12105,16 +12105,16 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>西邮</t>
+          <t>上海货盘</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>757.8144600000001</v>
+        <v>7547.36</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -12122,61 +12122,61 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="G165" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TSP</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>24297.43502</v>
+        <v>2266.86</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1706</v>
+        <v>2725</v>
       </c>
       <c r="G166" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>上海货盘</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>4612</v>
+        <v>1599.84</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -12193,60 +12193,60 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>上海货盘</t>
+          <t>奥韵汇</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>22137.76</v>
+        <v>11170.955</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>55</v>
+        <v>6864</v>
       </c>
       <c r="G168" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>易达云</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>625.89</v>
+        <v>47.725</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1435</v>
+        <v>1</v>
       </c>
       <c r="G169" t="n">
         <v>1</v>
@@ -12255,60 +12255,60 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>西邮</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1158.42</v>
+        <v>757.8144600000001</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>奥韵汇</t>
+          <t>额外过关服务费</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>12321.804</v>
+        <v>3796</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>10027</v>
+        <v>2</v>
       </c>
       <c r="G171" t="n">
         <v>2</v>
@@ -12322,27 +12322,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>易达云</t>
+          <t>TSP</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>175.83</v>
+        <v>24297.43502</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>1706</v>
       </c>
       <c r="G172" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173">
@@ -12353,24 +12353,24 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>易领</t>
+          <t>mic</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>2911.7467</v>
+        <v>5190.32569326269</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G173" t="n">
         <v>1</v>
@@ -12384,33 +12384,33 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>津达</t>
+          <t>上海货盘</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>78069.496</v>
+        <v>4612</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>19369</v>
+        <v>2</v>
       </c>
       <c r="G174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -12424,7 +12424,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-600.75</v>
+        <v>22137.76</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -12432,40 +12432,288 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="G175" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>东方嘉盛</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>625.89</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>1435</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1158.42</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>3</v>
+      </c>
+      <c r="G177" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>奥韵汇</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>12321.804</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>10027</v>
+      </c>
+      <c r="G178" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>易达云</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>175.83</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>易领</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>2911.7467</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>4</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>津达</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>78069.496</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>19369</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>上海货盘</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>-600.75</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>6</v>
+      </c>
+      <c r="G182" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
         <is>
           <t>久喜</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="D176" t="n">
+      <c r="D183" t="n">
         <v>5600735.95</v>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="E183" t="inlineStr">
         <is>
           <t>JPY</t>
         </is>
       </c>
-      <c r="F176" t="n">
+      <c r="F183" t="n">
         <v>381</v>
       </c>
-      <c r="G176" t="n">
+      <c r="G183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>酷麓</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1532.519</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>963</v>
+      </c>
+      <c r="G184" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13258,10 +13506,10 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>38715.788</v>
+        <v>74850.10316</v>
       </c>
       <c r="E30" t="n">
-        <v>-38715.788</v>
+        <v>-74850.10316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -13466,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>80275.60000000001</v>
+        <v>85465.60000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>-80275.60000000001</v>
+        <v>-85465.60000000001</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -13726,10 +13974,10 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>142332.07</v>
+        <v>143132.07</v>
       </c>
       <c r="E48" t="n">
-        <v>-142332.07</v>
+        <v>-143132.07</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -14272,10 +14520,10 @@
         <v>701.63</v>
       </c>
       <c r="D69" t="n">
-        <v>32289.709</v>
+        <v>33921.709</v>
       </c>
       <c r="E69" t="n">
-        <v>-31588.079</v>
+        <v>-33220.079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -14402,10 +14650,10 @@
         <v>1364.3</v>
       </c>
       <c r="D74" t="n">
-        <v>30526.432</v>
+        <v>36395.12396</v>
       </c>
       <c r="E74" t="n">
-        <v>-29162.132</v>
+        <v>-35030.82396</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -14480,10 +14728,10 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>761.91</v>
+        <v>1015.88</v>
       </c>
       <c r="E77" t="n">
-        <v>-761.91</v>
+        <v>-1015.88</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -14532,10 +14780,10 @@
         <v>18787.14</v>
       </c>
       <c r="D79" t="n">
-        <v>11172.874</v>
+        <v>17075.4319034</v>
       </c>
       <c r="E79" t="n">
-        <v>7614.266</v>
+        <v>1711.7080966</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -14584,10 +14832,10 @@
         <v>32887.61</v>
       </c>
       <c r="D81" t="n">
-        <v>17871.9236360896</v>
+        <v>18229.6736360896</v>
       </c>
       <c r="E81" t="n">
-        <v>15015.6863639104</v>
+        <v>14657.9363639104</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -14688,10 +14936,10 @@
         <v>12927.97</v>
       </c>
       <c r="D85" t="n">
-        <v>15826.535</v>
+        <v>21197.292690425</v>
       </c>
       <c r="E85" t="n">
-        <v>-2898.565</v>
+        <v>-8269.322690425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -14766,10 +15014,10 @@
         <v>69200.99000000001</v>
       </c>
       <c r="D88" t="n">
-        <v>10441.89946</v>
+        <v>14237.89946</v>
       </c>
       <c r="E88" t="n">
-        <v>58759.09054</v>
+        <v>54963.09054</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -14818,10 +15066,10 @@
         <v>1223.32</v>
       </c>
       <c r="D90" t="n">
-        <v>90391.3</v>
+        <v>95581.62569326269</v>
       </c>
       <c r="E90" t="n">
-        <v>-89167.98</v>
+        <v>-94358.30569326269</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -14922,14 +15170,14 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>-600.75</v>
+        <v>931.769</v>
       </c>
       <c r="E94" t="n">
-        <v>600.75</v>
+        <v>-931.769</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>不含SKU采购成本（原币种）</t>
+          <t>⚠️ 该月该币种无平台收入数据</t>
         </is>
       </c>
     </row>
@@ -16163,7 +16411,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>80275.60000000001</v>
+        <v>85465.60000000001</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -16171,10 +16419,10 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -16487,7 +16735,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>125487.59</v>
+        <v>126287.59</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -16495,10 +16743,10 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -19430,7 +19678,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10623.84</v>
+        <v>15813.84</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -19448,7 +19696,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>101875.6</v>
+        <v>107065.6</v>
       </c>
     </row>
     <row r="26">
@@ -19886,7 +20134,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>7374</v>
+        <v>8174</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -19928,7 +20176,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>125487.59</v>
+        <v>126287.59</v>
       </c>
     </row>
     <row r="34">
